--- a/experiment3/data_processing/exp_data/07_no_outliers.xlsx
+++ b/experiment3/data_processing/exp_data/07_no_outliers.xlsx
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>770.2692307692307</v>
+        <v>768.5833333333334</v>
       </c>
     </row>
     <row r="60">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>448.5625</v>
+        <v>449.0333333333334</v>
       </c>
     </row>
     <row r="74">
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>413.4285714285714</v>
+        <v>405.4444444444445</v>
       </c>
     </row>
     <row r="86">
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>690.64</v>
+        <v>643.5909090909091</v>
       </c>
     </row>
     <row r="146">
